--- a/data/trans_orig/Q64A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio que lleva trabajando en su empresa (en meses)</t>
+          <t>Tiempo medio que lleva trabajando en su empresa (en meses) (tasa de respuesta: 97,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>102,98; 126,25</t>
+          <t>103,06; 126,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>112,32; 141,88</t>
+          <t>112,99; 142,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108,93; 140,88</t>
+          <t>110,87; 139,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132,74; 161,05</t>
+          <t>132,0; 162,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>53,72; 77,8</t>
+          <t>52,98; 78,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,35; 105,17</t>
+          <t>74,44; 105,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,27; 103,87</t>
+          <t>75,91; 101,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>99,77; 121,44</t>
+          <t>101,17; 121,84</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,07; 108,93</t>
+          <t>91,34; 110,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>102,24; 124,83</t>
+          <t>101,85; 123,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99,36; 120,3</t>
+          <t>100,12; 120,35</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>121,04; 141,19</t>
+          <t>122,67; 142,56</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,27; 112,99</t>
+          <t>94,56; 114,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111,55; 134,68</t>
+          <t>111,59; 135,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104,4; 128,83</t>
+          <t>103,81; 128,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42,05; 143,13</t>
+          <t>45,51; 141,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,45; 88,39</t>
+          <t>65,69; 89,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>71,2; 94,73</t>
+          <t>70,13; 94,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,85; 100,8</t>
+          <t>77,99; 101,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>100,02; 116,94</t>
+          <t>99,81; 117,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,52; 102,53</t>
+          <t>87,0; 101,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98,12; 114,95</t>
+          <t>98,2; 115,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,71; 113,86</t>
+          <t>95,94; 113,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,07; 128,47</t>
+          <t>53,9; 128,42</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102,25; 124,02</t>
+          <t>103,77; 125,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118,21; 146,36</t>
+          <t>117,54; 146,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,02; 116,02</t>
+          <t>92,38; 115,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128,06; 156,67</t>
+          <t>127,96; 158,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>56,47; 80,86</t>
+          <t>57,72; 80,81</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,39; 103,5</t>
+          <t>76,78; 103,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,91; 82,49</t>
+          <t>64,42; 82,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>106,61; 129,66</t>
+          <t>107,62; 130,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,84; 107,26</t>
+          <t>89,67; 105,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104,09; 124,57</t>
+          <t>104,55; 126,62</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>83,43; 99,14</t>
+          <t>82,55; 98,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122,09; 141,83</t>
+          <t>122,0; 141,67</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>88,21; 104,47</t>
+          <t>87,82; 104,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>113,9; 138,59</t>
+          <t>114,15; 137,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115,43; 138,62</t>
+          <t>114,96; 139,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>136,18; 160,42</t>
+          <t>135,68; 160,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>68,15; 87,35</t>
+          <t>67,56; 85,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,67; 100,32</t>
+          <t>78,21; 100,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,74; 126,06</t>
+          <t>99,3; 124,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>86,9; 133,56</t>
+          <t>83,45; 133,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>82,34; 94,65</t>
+          <t>81,54; 94,4</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102,06; 118,87</t>
+          <t>102,54; 119,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>112,03; 129,74</t>
+          <t>111,99; 129,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>109,57; 143,18</t>
+          <t>108,33; 143,13</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>100,34; 109,91</t>
+          <t>100,63; 110,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>120,03; 132,41</t>
+          <t>120,49; 133,35</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110,99; 123,09</t>
+          <t>110,9; 122,97</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76,02; 145,69</t>
+          <t>81,66; 145,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,85; 78,58</t>
+          <t>67,59; 78,73</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,29; 92,92</t>
+          <t>80,36; 93,07</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,53; 97,52</t>
+          <t>85,62; 97,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98,68; 119,31</t>
+          <t>98,67; 119,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,5; 98,07</t>
+          <t>90,55; 98,13</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105,29; 114,85</t>
+          <t>105,55; 114,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102,3; 111,09</t>
+          <t>102,04; 110,7</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,53; 131,89</t>
+          <t>83,53; 131,26</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q64A_R-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>146,84</t>
+          <t>145,69</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>110,78</t>
+          <t>109,71</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>131,61</t>
+          <t>130,57</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>103,06; 126,27</t>
+          <t>102,11; 125,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>112,99; 142,4</t>
+          <t>111,46; 140,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110,87; 139,81</t>
+          <t>109,7; 139,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132,0; 162,09</t>
+          <t>131,24; 160,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>52,98; 78,48</t>
+          <t>54,25; 80,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>74,44; 105,96</t>
+          <t>73,23; 104,54</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,91; 101,29</t>
+          <t>75,16; 102,66</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>101,17; 121,84</t>
+          <t>99,2; 121,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>91,34; 110,03</t>
+          <t>91,54; 110,14</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>101,85; 123,48</t>
+          <t>101,46; 122,99</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>100,12; 120,35</t>
+          <t>99,51; 121,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>122,67; 142,56</t>
+          <t>121,05; 139,59</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95,96</t>
+          <t>133,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>108,1</t>
+          <t>105,26</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>99,97</t>
+          <t>121,62</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,56; 114,57</t>
+          <t>94,26; 113,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>111,59; 135,16</t>
+          <t>109,44; 133,99</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>103,81; 128,34</t>
+          <t>104,85; 127,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,51; 141,72</t>
+          <t>122,4; 144,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>65,69; 89,36</t>
+          <t>65,5; 87,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,13; 94,25</t>
+          <t>70,39; 93,76</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>77,99; 101,33</t>
+          <t>76,95; 101,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>99,81; 117,3</t>
+          <t>97,28; 113,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87,0; 101,46</t>
+          <t>87,24; 101,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98,2; 115,37</t>
+          <t>97,79; 114,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95,94; 113,02</t>
+          <t>96,16; 113,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>53,9; 128,42</t>
+          <t>114,29; 128,78</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>142,41</t>
+          <t>129,71</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>118,13</t>
+          <t>114,5</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>131,46</t>
+          <t>122,88</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>103,77; 125,07</t>
+          <t>102,59; 125,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>117,54; 146,62</t>
+          <t>118,41; 146,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>92,38; 115,3</t>
+          <t>92,45; 114,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>127,96; 158,33</t>
+          <t>117,2; 143,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>57,72; 80,81</t>
+          <t>58,13; 81,82</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,78; 103,17</t>
+          <t>75,49; 102,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>64,42; 82,54</t>
+          <t>64,97; 82,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>107,62; 130,89</t>
+          <t>104,34; 126,26</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>89,67; 105,87</t>
+          <t>89,73; 106,52</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>104,55; 126,62</t>
+          <t>103,69; 124,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>82,55; 98,29</t>
+          <t>83,11; 98,31</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>122,0; 141,67</t>
+          <t>114,79; 131,46</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148,26</t>
+          <t>140,18</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>115,66</t>
+          <t>125,43</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>131,72</t>
+          <t>133,33</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>87,82; 104,15</t>
+          <t>87,76; 104,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>114,15; 137,66</t>
+          <t>114,75; 138,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114,96; 139,76</t>
+          <t>114,97; 138,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>135,68; 160,36</t>
+          <t>128,61; 151,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>67,56; 85,53</t>
+          <t>68,7; 86,39</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,21; 100,69</t>
+          <t>78,53; 99,91</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,3; 124,43</t>
+          <t>100,11; 125,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>83,45; 133,67</t>
+          <t>115,47; 135,5</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>81,54; 94,4</t>
+          <t>82,38; 94,3</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>102,54; 119,53</t>
+          <t>102,27; 118,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111,99; 129,44</t>
+          <t>111,86; 128,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>108,33; 143,13</t>
+          <t>125,5; 140,46</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125,25</t>
+          <t>136,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>113,16</t>
+          <t>114,09</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>120,19</t>
+          <t>126,8</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>100,63; 110,69</t>
+          <t>100,94; 110,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>120,49; 133,35</t>
+          <t>119,12; 132,65</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110,9; 122,97</t>
+          <t>111,33; 123,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81,66; 145,29</t>
+          <t>130,74; 142,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,59; 78,73</t>
+          <t>67,54; 78,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,36; 93,07</t>
+          <t>80,14; 92,21</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,62; 97,52</t>
+          <t>85,77; 97,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>98,67; 119,3</t>
+          <t>108,99; 119,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>90,55; 98,13</t>
+          <t>90,49; 98,06</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105,55; 114,71</t>
+          <t>105,17; 114,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102,04; 110,7</t>
+          <t>101,7; 110,55</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>83,53; 131,26</t>
+          <t>122,73; 131,03</t>
         </is>
       </c>
     </row>
